--- a/Reporte_Final_Clientes.xlsx
+++ b/Reporte_Final_Clientes.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,31 +425,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>nombre_cliente</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>monto</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>tipo_solicitud</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>mensaje_original</t>
         </is>
@@ -446,40 +458,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>María González</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>500</v>
-      </c>
+          <t>Ana Rodríguez</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Queja</t>
+          <t>Venta</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Es el colmo, llevo esperando mi reembolso de 500 pesos desde ayer. Soy María González.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Venta</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Buenas tardes, me interesa saber el precio de sus servicios de limpieza de oficinas.</t>
+          <t>¡Hola! Me gustaría cotizar 10 licencias de software para mi equipo de diseño. Somos la agencia "Creativos SA". Mi nombre es Ana Rodríguez y necesitamos la propuesta antes del próximo viernes. Gracias.</t>
         </is>
       </c>
     </row>
